--- a/vignettes/vignette-2/target_transition_table.xlsx
+++ b/vignettes/vignette-2/target_transition_table.xlsx
@@ -546,10 +546,10 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>491</v>
+        <v>789</v>
       </c>
       <c r="O2" t="n">
-        <v>285</v>
+        <v>453</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-2/target_transition_table.xlsx
+++ b/vignettes/vignette-2/target_transition_table.xlsx
@@ -546,10 +546,10 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>789</v>
+        <v>726</v>
       </c>
       <c r="O2" t="n">
-        <v>453</v>
+        <v>430</v>
       </c>
     </row>
   </sheetData>
